--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fondos - Datos Completos" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clasificación por Rating" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen Estadístico" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historial" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -90,6 +91,10 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -154,7 +159,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -176,11 +181,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -315,6 +364,24 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -680,8 +747,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:AN38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -718,6 +785,11 @@
     <col width="7" customWidth="1" min="33" max="33"/>
     <col width="9" customWidth="1" min="34" max="34"/>
     <col width="35" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="10" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
+    <col width="10" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -735,18 +807,18 @@
           <t>DATOS BÁSICOS</t>
         </is>
       </c>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
+      <c r="G1" s="46" t="n"/>
+      <c r="H1" s="47" t="n"/>
       <c r="I1" s="4" t="inlineStr">
         <is>
           <t>VENCIMIENTO (% Plazo)</t>
         </is>
       </c>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
+      <c r="J1" s="46" t="n"/>
+      <c r="K1" s="46" t="n"/>
+      <c r="L1" s="46" t="n"/>
+      <c r="M1" s="46" t="n"/>
+      <c r="N1" s="47" t="n"/>
       <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Total
@@ -758,12 +830,12 @@
           <t>CALIDAD CREDITICIA (%)</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="2" t="n"/>
-      <c r="S1" s="2" t="n"/>
-      <c r="T1" s="2" t="n"/>
-      <c r="U1" s="2" t="n"/>
-      <c r="V1" s="2" t="n"/>
+      <c r="Q1" s="46" t="n"/>
+      <c r="R1" s="46" t="n"/>
+      <c r="S1" s="46" t="n"/>
+      <c r="T1" s="46" t="n"/>
+      <c r="U1" s="46" t="n"/>
+      <c r="V1" s="47" t="n"/>
       <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Total
@@ -775,16 +847,16 @@
           <t>RENTABILIDAD</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="n"/>
+      <c r="Y1" s="47" t="n"/>
       <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>GEOGRAFÍA (%)</t>
         </is>
       </c>
-      <c r="AA1" s="2" t="n"/>
-      <c r="AB1" s="2" t="n"/>
-      <c r="AC1" s="2" t="n"/>
-      <c r="AD1" s="2" t="n"/>
+      <c r="AA1" s="46" t="n"/>
+      <c r="AB1" s="46" t="n"/>
+      <c r="AC1" s="46" t="n"/>
+      <c r="AD1" s="47" t="n"/>
       <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Total
@@ -796,7 +868,7 @@
           <t>EXPOSICIÓN</t>
         </is>
       </c>
-      <c r="AG1" s="2" t="n"/>
+      <c r="AG1" s="47" t="n"/>
       <c r="AH1" s="3" t="inlineStr">
         <is>
           <t>⭐</t>
@@ -996,6 +1068,36 @@
           <t>Notas Importantes</t>
         </is>
       </c>
+      <c r="AJ2" s="6" t="inlineStr">
+        <is>
+          <t>NAV
+Último</t>
+        </is>
+      </c>
+      <c r="AK2" s="6" t="inlineStr">
+        <is>
+          <t>Rent.
+1 Mes</t>
+        </is>
+      </c>
+      <c r="AL2" s="6" t="inlineStr">
+        <is>
+          <t>Rent.
+3 Meses</t>
+        </is>
+      </c>
+      <c r="AM2" s="6" t="inlineStr">
+        <is>
+          <t>Rent.
+1 Año</t>
+        </is>
+      </c>
+      <c r="AN2" s="6" t="inlineStr">
+        <is>
+          <t>Última
+Actualiz.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
@@ -1076,8 +1178,8 @@
       <c r="X3" s="11" t="n">
         <v>0.0275</v>
       </c>
-      <c r="Y3" s="11" t="n">
-        <v>0.0025</v>
+      <c r="Y3" s="48" t="n">
+        <v>0.0143</v>
       </c>
       <c r="Z3" s="9" t="n"/>
       <c r="AA3" s="9" t="n"/>
@@ -1089,12 +1191,26 @@
       </c>
       <c r="AF3" s="9" t="n"/>
       <c r="AG3" s="9" t="n"/>
-      <c r="AH3" s="9" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
+      <c r="AH3" s="49" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="AI3" s="12" t="inlineStr"/>
+      <c r="AK3" s="48" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="AL3" s="48" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="AM3" s="48" t="n">
+        <v>0.0701</v>
+      </c>
+      <c r="AN3" s="49" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="13" t="inlineStr">
@@ -1148,6 +1264,11 @@
       <c r="AG4" s="14" t="n"/>
       <c r="AH4" s="14" t="n"/>
       <c r="AI4" s="16" t="n"/>
+      <c r="AN4" s="50" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
@@ -1229,6 +1350,11 @@
         </is>
       </c>
       <c r="AI5" s="12" t="inlineStr"/>
+      <c r="AN5" s="49" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
@@ -1338,6 +1464,11 @@
         </is>
       </c>
       <c r="AI6" s="16" t="inlineStr"/>
+      <c r="AN6" s="50" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
@@ -1425,6 +1556,11 @@
         </is>
       </c>
       <c r="AI7" s="12" t="inlineStr"/>
+      <c r="AN7" s="49" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="13" t="inlineStr">
@@ -1536,6 +1672,11 @@
         </is>
       </c>
       <c r="AI8" s="16" t="inlineStr"/>
+      <c r="AN8" s="50" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
@@ -1589,6 +1730,11 @@
       <c r="AG9" s="9" t="n"/>
       <c r="AH9" s="9" t="n"/>
       <c r="AI9" s="12" t="n"/>
+      <c r="AN9" s="49" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="13" t="inlineStr">
@@ -1759,6 +1905,11 @@
         </is>
       </c>
       <c r="AI11" s="12" t="inlineStr"/>
+      <c r="AN11" s="49" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="13" t="inlineStr">
@@ -1860,6 +2011,11 @@
         </is>
       </c>
       <c r="AI12" s="16" t="inlineStr"/>
+      <c r="AN12" s="50" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
@@ -1913,6 +2069,11 @@
       <c r="AG13" s="9" t="n"/>
       <c r="AH13" s="9" t="n"/>
       <c r="AI13" s="12" t="n"/>
+      <c r="AN13" s="49" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="13" t="inlineStr">
@@ -1966,6 +2127,11 @@
       <c r="AG14" s="14" t="n"/>
       <c r="AH14" s="14" t="n"/>
       <c r="AI14" s="16" t="n"/>
+      <c r="AN14" s="50" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
@@ -2069,6 +2235,11 @@
       <c r="AG15" s="9" t="n"/>
       <c r="AH15" s="9" t="n"/>
       <c r="AI15" s="12" t="inlineStr"/>
+      <c r="AN15" s="49" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="13" t="inlineStr">
@@ -2092,8 +2263,8 @@
           <t>LU</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n">
-        <v>1.49</v>
+      <c r="F16" s="51" t="n">
+        <v>3.07204</v>
       </c>
       <c r="G16" s="17" t="n">
         <v>0.036</v>
@@ -2151,8 +2322,8 @@
       <c r="X16" s="17" t="n">
         <v>0.028</v>
       </c>
-      <c r="Y16" s="17" t="n">
-        <v>0.003</v>
+      <c r="Y16" s="52" t="n">
+        <v>-0.0035</v>
       </c>
       <c r="Z16" s="15" t="n">
         <v>0.53</v>
@@ -2178,12 +2349,26 @@
       <c r="AG16" s="15" t="n">
         <v>0.44</v>
       </c>
-      <c r="AH16" s="14" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
+      <c r="AH16" s="50" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="AI16" s="16" t="inlineStr"/>
+      <c r="AK16" s="52" t="n">
+        <v>-0.0109</v>
+      </c>
+      <c r="AL16" s="52" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="AM16" s="52" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="AN16" s="50" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
@@ -2295,6 +2480,11 @@
         </is>
       </c>
       <c r="AI17" s="12" t="inlineStr"/>
+      <c r="AN17" s="49" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
@@ -2382,6 +2572,11 @@
       <c r="AG18" s="14" t="n"/>
       <c r="AH18" s="14" t="n"/>
       <c r="AI18" s="16" t="inlineStr"/>
+      <c r="AN18" s="50" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
@@ -2475,6 +2670,11 @@
       <c r="AG19" s="9" t="n"/>
       <c r="AH19" s="9" t="n"/>
       <c r="AI19" s="12" t="inlineStr"/>
+      <c r="AN19" s="49" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="13" t="inlineStr">
@@ -2545,8 +2745,8 @@
       <c r="X20" s="17" t="n">
         <v>0.0432</v>
       </c>
-      <c r="Y20" s="17" t="n">
-        <v>0.002</v>
+      <c r="Y20" s="52" t="n">
+        <v>-0.066</v>
       </c>
       <c r="Z20" s="15" t="n">
         <v>0.46</v>
@@ -2568,14 +2768,28 @@
       </c>
       <c r="AF20" s="14" t="n"/>
       <c r="AG20" s="14" t="n"/>
-      <c r="AH20" s="14" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
+      <c r="AH20" s="50" t="inlineStr">
+        <is>
+          <t>⭐</t>
         </is>
       </c>
       <c r="AI20" s="16" t="inlineStr">
         <is>
           <t>2 gestores: AAA Citywire</t>
+        </is>
+      </c>
+      <c r="AK20" s="52" t="n">
+        <v>-0.066</v>
+      </c>
+      <c r="AL20" s="52" t="n">
+        <v>-0.0512</v>
+      </c>
+      <c r="AM20" s="52" t="n">
+        <v>-0.0274</v>
+      </c>
+      <c r="AN20" s="50" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
         </is>
       </c>
     </row>
@@ -2689,6 +2903,11 @@
         </is>
       </c>
       <c r="AI21" s="12" t="inlineStr"/>
+      <c r="AN21" s="49" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="13" t="inlineStr">
@@ -2768,6 +2987,11 @@
         </is>
       </c>
       <c r="AI22" s="16" t="inlineStr"/>
+      <c r="AN22" s="50" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
@@ -2885,6 +3109,11 @@
       <c r="AI23" s="12" t="inlineStr">
         <is>
           <t>Objetivo €str+1,80% (2024: conseguido €str+0,20)</t>
+        </is>
+      </c>
+      <c r="AN23" s="49" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
         </is>
       </c>
     </row>
@@ -2986,6 +3215,11 @@
         </is>
       </c>
       <c r="AI24" s="16" t="inlineStr"/>
+      <c r="AN24" s="50" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
@@ -3089,6 +3323,11 @@
       <c r="AG25" s="9" t="n"/>
       <c r="AH25" s="9" t="n"/>
       <c r="AI25" s="12" t="inlineStr"/>
+      <c r="AN25" s="49" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="13" t="inlineStr">
@@ -3206,6 +3445,11 @@
       <c r="AI26" s="16" t="inlineStr">
         <is>
           <t>100% servicios financieros, 50% COCOs</t>
+        </is>
+      </c>
+      <c r="AN26" s="50" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3514,9 @@
         <v>0.97</v>
       </c>
       <c r="X27" s="9" t="n"/>
-      <c r="Y27" s="9" t="n"/>
+      <c r="Y27" s="48" t="n">
+        <v>0.0101</v>
+      </c>
       <c r="Z27" s="9" t="n"/>
       <c r="AA27" s="9" t="n"/>
       <c r="AB27" s="9" t="n"/>
@@ -3281,8 +3527,26 @@
       </c>
       <c r="AF27" s="9" t="n"/>
       <c r="AG27" s="9" t="n"/>
-      <c r="AH27" s="9" t="n"/>
+      <c r="AH27" s="49" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
       <c r="AI27" s="12" t="inlineStr"/>
+      <c r="AK27" s="48" t="n">
+        <v>-0.0491</v>
+      </c>
+      <c r="AL27" s="48" t="n">
+        <v>0.0447</v>
+      </c>
+      <c r="AM27" s="48" t="n">
+        <v>0.0688</v>
+      </c>
+      <c r="AN27" s="49" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="13" t="inlineStr">
@@ -3380,6 +3644,11 @@
       <c r="AG28" s="14" t="n"/>
       <c r="AH28" s="14" t="n"/>
       <c r="AI28" s="16" t="inlineStr"/>
+      <c r="AN28" s="50" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
@@ -3487,6 +3756,11 @@
       <c r="AG29" s="9" t="n"/>
       <c r="AH29" s="9" t="n"/>
       <c r="AI29" s="12" t="inlineStr"/>
+      <c r="AN29" s="49" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="13" t="inlineStr">
@@ -3596,6 +3870,11 @@
       <c r="AG30" s="14" t="n"/>
       <c r="AH30" s="14" t="n"/>
       <c r="AI30" s="16" t="inlineStr"/>
+      <c r="AN30" s="50" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
@@ -3703,6 +3982,11 @@
       <c r="AG31" s="9" t="n"/>
       <c r="AH31" s="9" t="n"/>
       <c r="AI31" s="12" t="inlineStr"/>
+      <c r="AN31" s="49" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="13" t="inlineStr">
@@ -3785,8 +4069,8 @@
       <c r="X32" s="17" t="n">
         <v>0.0722</v>
       </c>
-      <c r="Y32" s="17" t="n">
-        <v>0.0043</v>
+      <c r="Y32" s="52" t="n">
+        <v>-0.0098</v>
       </c>
       <c r="Z32" s="15" t="n">
         <v>0.4</v>
@@ -3814,6 +4098,20 @@
         </is>
       </c>
       <c r="AI32" s="16" t="inlineStr"/>
+      <c r="AK32" s="52" t="n">
+        <v>-0.0141</v>
+      </c>
+      <c r="AL32" s="52" t="n">
+        <v>-0.006999999999999999</v>
+      </c>
+      <c r="AM32" s="52" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="AN32" s="50" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
@@ -3865,6 +4163,11 @@
       <c r="AG33" s="9" t="n"/>
       <c r="AH33" s="9" t="n"/>
       <c r="AI33" s="12" t="n"/>
+      <c r="AN33" s="49" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="13" t="inlineStr">
@@ -3980,6 +4283,11 @@
           <t>Países emergentes. Para diversificar geográficamente</t>
         </is>
       </c>
+      <c r="AN34" s="50" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
@@ -4087,6 +4395,11 @@
         </is>
       </c>
       <c r="AI35" s="12" t="inlineStr"/>
+      <c r="AN35" s="49" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="13" t="inlineStr">
@@ -4141,8 +4454,8 @@
       <c r="X36" s="17" t="n">
         <v>0.0194</v>
       </c>
-      <c r="Y36" s="17" t="n">
-        <v>0.0019</v>
+      <c r="Y36" s="52" t="n">
+        <v>-0.0046</v>
       </c>
       <c r="Z36" s="14" t="n"/>
       <c r="AA36" s="14" t="n"/>
@@ -4154,12 +4467,26 @@
       </c>
       <c r="AF36" s="14" t="n"/>
       <c r="AG36" s="14" t="n"/>
-      <c r="AH36" s="14" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
+      <c r="AH36" s="50" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="AI36" s="16" t="inlineStr"/>
+      <c r="AK36" s="52" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="AL36" s="52" t="n">
+        <v>0.005500000000000001</v>
+      </c>
+      <c r="AM36" s="52" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="AN36" s="50" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
@@ -4253,6 +4580,11 @@
       <c r="AG37" s="9" t="n"/>
       <c r="AH37" s="9" t="n"/>
       <c r="AI37" s="12" t="inlineStr"/>
+      <c r="AN37" s="49" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="13" t="inlineStr">
@@ -4364,6 +4696,11 @@
         </is>
       </c>
       <c r="AI38" s="16" t="inlineStr"/>
+      <c r="AN38" s="50" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4385,7 +4722,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I49"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -5796,7 +6133,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -5810,9 +6147,9 @@
           <t>RESUMEN ESTADÍSTICO — FONDOS DE INVERSIÓN</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
+      <c r="B1" s="46" t="n"/>
+      <c r="C1" s="46" t="n"/>
+      <c r="D1" s="47" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -5826,9 +6163,9 @@
           <t>DISTRIBUCIÓN POR CALIDAD CREDITICIA</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
+      <c r="B3" s="46" t="n"/>
+      <c r="C3" s="46" t="n"/>
+      <c r="D3" s="47" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="42" t="inlineStr">
@@ -5926,4 +6263,50 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="53" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B1" s="53" t="inlineStr">
+        <is>
+          <t>Fondos actualizados</t>
+        </is>
+      </c>
+      <c r="C1" s="53" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Actualización automática diaria v3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -229,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -382,6 +382,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1178,7 +1187,7 @@
       <c r="X3" s="11" t="n">
         <v>0.0275</v>
       </c>
-      <c r="Y3" s="48" t="n">
+      <c r="Y3" s="54" t="n">
         <v>0.0143</v>
       </c>
       <c r="Z3" s="9" t="n"/>
@@ -1197,13 +1206,13 @@
         </is>
       </c>
       <c r="AI3" s="12" t="inlineStr"/>
-      <c r="AK3" s="48" t="n">
+      <c r="AK3" s="55" t="n">
         <v>-0.013</v>
       </c>
-      <c r="AL3" s="48" t="n">
+      <c r="AL3" s="54" t="n">
         <v>0.0215</v>
       </c>
-      <c r="AM3" s="48" t="n">
+      <c r="AM3" s="54" t="n">
         <v>0.0701</v>
       </c>
       <c r="AN3" s="49" t="inlineStr">
@@ -2322,7 +2331,7 @@
       <c r="X16" s="17" t="n">
         <v>0.028</v>
       </c>
-      <c r="Y16" s="52" t="n">
+      <c r="Y16" s="55" t="n">
         <v>-0.0035</v>
       </c>
       <c r="Z16" s="15" t="n">
@@ -2355,13 +2364,13 @@
         </is>
       </c>
       <c r="AI16" s="16" t="inlineStr"/>
-      <c r="AK16" s="52" t="n">
+      <c r="AK16" s="55" t="n">
         <v>-0.0109</v>
       </c>
-      <c r="AL16" s="52" t="n">
+      <c r="AL16" s="55" t="n">
         <v>-0.0023</v>
       </c>
-      <c r="AM16" s="52" t="n">
+      <c r="AM16" s="54" t="n">
         <v>0.026</v>
       </c>
       <c r="AN16" s="50" t="inlineStr">
@@ -2745,7 +2754,7 @@
       <c r="X20" s="17" t="n">
         <v>0.0432</v>
       </c>
-      <c r="Y20" s="52" t="n">
+      <c r="Y20" s="56" t="n">
         <v>-0.066</v>
       </c>
       <c r="Z20" s="15" t="n">
@@ -2778,13 +2787,13 @@
           <t>2 gestores: AAA Citywire</t>
         </is>
       </c>
-      <c r="AK20" s="52" t="n">
+      <c r="AK20" s="55" t="n">
         <v>-0.066</v>
       </c>
-      <c r="AL20" s="52" t="n">
+      <c r="AL20" s="55" t="n">
         <v>-0.0512</v>
       </c>
-      <c r="AM20" s="52" t="n">
+      <c r="AM20" s="55" t="n">
         <v>-0.0274</v>
       </c>
       <c r="AN20" s="50" t="inlineStr">
@@ -3514,7 +3523,7 @@
         <v>0.97</v>
       </c>
       <c r="X27" s="9" t="n"/>
-      <c r="Y27" s="48" t="n">
+      <c r="Y27" s="54" t="n">
         <v>0.0101</v>
       </c>
       <c r="Z27" s="9" t="n"/>
@@ -3533,13 +3542,13 @@
         </is>
       </c>
       <c r="AI27" s="12" t="inlineStr"/>
-      <c r="AK27" s="48" t="n">
+      <c r="AK27" s="55" t="n">
         <v>-0.0491</v>
       </c>
-      <c r="AL27" s="48" t="n">
+      <c r="AL27" s="54" t="n">
         <v>0.0447</v>
       </c>
-      <c r="AM27" s="48" t="n">
+      <c r="AM27" s="54" t="n">
         <v>0.0688</v>
       </c>
       <c r="AN27" s="49" t="inlineStr">
@@ -4069,7 +4078,7 @@
       <c r="X32" s="17" t="n">
         <v>0.0722</v>
       </c>
-      <c r="Y32" s="52" t="n">
+      <c r="Y32" s="55" t="n">
         <v>-0.0098</v>
       </c>
       <c r="Z32" s="15" t="n">
@@ -4098,13 +4107,13 @@
         </is>
       </c>
       <c r="AI32" s="16" t="inlineStr"/>
-      <c r="AK32" s="52" t="n">
+      <c r="AK32" s="55" t="n">
         <v>-0.0141</v>
       </c>
-      <c r="AL32" s="52" t="n">
+      <c r="AL32" s="55" t="n">
         <v>-0.006999999999999999</v>
       </c>
-      <c r="AM32" s="52" t="n">
+      <c r="AM32" s="54" t="n">
         <v>0.0351</v>
       </c>
       <c r="AN32" s="50" t="inlineStr">
@@ -4454,7 +4463,7 @@
       <c r="X36" s="17" t="n">
         <v>0.0194</v>
       </c>
-      <c r="Y36" s="52" t="n">
+      <c r="Y36" s="55" t="n">
         <v>-0.0046</v>
       </c>
       <c r="Z36" s="14" t="n"/>
@@ -4473,13 +4482,13 @@
         </is>
       </c>
       <c r="AI36" s="16" t="inlineStr"/>
-      <c r="AK36" s="52" t="n">
+      <c r="AK36" s="54" t="n">
         <v>0.0131</v>
       </c>
-      <c r="AL36" s="52" t="n">
+      <c r="AL36" s="54" t="n">
         <v>0.005500000000000001</v>
       </c>
-      <c r="AM36" s="52" t="n">
+      <c r="AM36" s="54" t="n">
         <v>0.1146</v>
       </c>
       <c r="AN36" s="50" t="inlineStr">
@@ -6271,7 +6280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6306,6 +6315,26 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Amundi Euro Government Bonds (sin ID), Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURHDG), Amundi Funds Pioneer US Bond USD (sin ID), Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yield, Axa IM FIS US Corporate Interm. Bonds EURHDG, Axa Im Fiss Europe Short Duration High Yield, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Muzinich Enhanced Yield Short Term (sin ID), Neuberger Short Duration Emerg. Market EURHDG, Pimco Income EuroHDG, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Income EURHDG</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Actualización automática v4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -19,8 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -229,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -389,6 +390,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1206,6 +1210,9 @@
         </is>
       </c>
       <c r="AI3" s="12" t="inlineStr"/>
+      <c r="AJ3" s="57" t="n">
+        <v>831.74</v>
+      </c>
       <c r="AK3" s="55" t="n">
         <v>-0.013</v>
       </c>
@@ -6280,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6335,6 +6342,26 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Axa IM FIS US Corporate Interm. Bonds EU, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>v5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6362,6 +6362,26 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>v6 - búsqueda por ISIN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6382,6 +6382,26 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6402,6 +6402,26 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6422,6 +6422,26 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6442,6 +6442,26 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6462,6 +6462,26 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>19/03/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6482,6 +6482,26 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6502,6 +6502,26 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6522,6 +6522,26 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6542,6 +6542,26 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6562,6 +6562,26 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6582,6 +6582,26 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6602,6 +6602,26 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6622,6 +6622,26 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6642,6 +6642,26 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6662,6 +6662,26 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6682,6 +6682,26 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6702,6 +6702,26 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6722,6 +6722,26 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6742,6 +6742,26 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6762,6 +6762,26 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6782,6 +6782,26 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6802,6 +6802,26 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6822,6 +6822,26 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6842,6 +6842,26 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6862,6 +6862,26 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6882,6 +6882,26 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6902,6 +6902,26 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6922,6 +6922,26 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6942,6 +6942,26 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6962,6 +6962,26 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6982,6 +6982,26 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7002,6 +7002,26 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7022,6 +7022,26 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7042,6 +7042,26 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7062,6 +7062,26 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7082,6 +7082,26 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7102,6 +7102,26 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7122,6 +7122,26 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7142,6 +7142,26 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7162,6 +7162,26 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7182,6 +7182,26 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7202,6 +7202,26 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7222,6 +7222,26 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7242,6 +7242,26 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7262,6 +7262,26 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7282,6 +7282,26 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7302,6 +7302,26 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7322,6 +7322,26 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7342,6 +7342,26 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7362,6 +7362,26 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7382,6 +7382,26 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7402,6 +7402,26 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7422,6 +7422,26 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7442,6 +7442,26 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7462,6 +7462,26 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7482,6 +7482,26 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7502,6 +7502,26 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7522,6 +7522,26 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7542,6 +7542,26 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7562,6 +7562,26 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7582,6 +7582,26 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7602,6 +7602,26 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7622,6 +7622,26 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7642,6 +7642,26 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7662,6 +7662,26 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7682,6 +7682,26 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7702,6 +7702,26 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7722,6 +7722,26 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7742,6 +7742,26 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7762,6 +7762,26 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7782,6 +7782,26 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7802,6 +7802,26 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7822,6 +7822,26 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7842,6 +7842,26 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7862,6 +7862,26 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7882,6 +7882,26 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7902,6 +7902,26 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7922,6 +7922,26 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7942,6 +7942,26 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7962,6 +7962,26 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7982,6 +7982,26 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8002,6 +8002,26 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8022,6 +8022,26 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8042,6 +8042,26 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8062,6 +8062,26 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8082,6 +8082,26 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8102,6 +8102,26 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8122,6 +8122,26 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8142,6 +8142,26 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8162,6 +8162,26 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8182,6 +8182,26 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8202,6 +8202,26 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8222,6 +8222,26 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>22/07/2026</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D98"/>
+  <dimension ref="A1:D99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8242,6 +8242,26 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>23/07/2026</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8262,6 +8262,26 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8282,6 +8282,26 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8302,6 +8302,26 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8322,6 +8322,26 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D103"/>
+  <dimension ref="A1:D104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8342,6 +8342,26 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8362,6 +8362,26 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8382,6 +8382,26 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D106"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8402,6 +8402,26 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8422,6 +8422,26 @@
         </is>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D108"/>
+  <dimension ref="A1:D109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8442,6 +8442,26 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8462,6 +8462,26 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D110"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8482,6 +8482,26 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8502,6 +8502,26 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8522,6 +8522,26 @@
         </is>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D113"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8542,6 +8542,26 @@
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D114"/>
+  <dimension ref="A1:D115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8562,6 +8562,26 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D115"/>
+  <dimension ref="A1:D116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8582,6 +8582,26 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D116"/>
+  <dimension ref="A1:D117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8602,6 +8602,26 @@
         </is>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D117"/>
+  <dimension ref="A1:D118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8622,6 +8622,26 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D118"/>
+  <dimension ref="A1:D119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8642,6 +8642,26 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8662,6 +8662,26 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8682,6 +8682,26 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:D122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8702,6 +8702,26 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D122"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8722,6 +8722,26 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:D124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8742,6 +8742,26 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D124"/>
+  <dimension ref="A1:D125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8762,6 +8762,26 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D125"/>
+  <dimension ref="A1:D126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8782,6 +8782,26 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D126"/>
+  <dimension ref="A1:D127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8802,6 +8802,26 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D127"/>
+  <dimension ref="A1:D128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8822,6 +8822,26 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D128"/>
+  <dimension ref="A1:D129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8842,6 +8842,26 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D129"/>
+  <dimension ref="A1:D130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8862,6 +8862,26 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>0</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D130"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8882,6 +8882,26 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D131"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8902,6 +8902,26 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>0</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D132"/>
+  <dimension ref="A1:D133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8922,6 +8922,26 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>0</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fondos_inversion.xlsx
+++ b/fondos_inversion.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AN3" s="49" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="AI4" s="16" t="n"/>
       <c r="AN4" s="50" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="AI5" s="12" t="inlineStr"/>
       <c r="AN5" s="49" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       <c r="AI6" s="16" t="inlineStr"/>
       <c r="AN6" s="50" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="AI7" s="12" t="inlineStr"/>
       <c r="AN7" s="49" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       <c r="AI8" s="16" t="inlineStr"/>
       <c r="AN8" s="50" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="AI9" s="12" t="n"/>
       <c r="AN9" s="49" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       <c r="AI11" s="12" t="inlineStr"/>
       <c r="AN11" s="49" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       <c r="AI12" s="16" t="inlineStr"/>
       <c r="AN12" s="50" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="AI13" s="12" t="n"/>
       <c r="AN13" s="49" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       <c r="AI14" s="16" t="n"/>
       <c r="AN14" s="50" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       <c r="AI15" s="12" t="inlineStr"/>
       <c r="AN15" s="49" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AN16" s="50" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       <c r="AI17" s="12" t="inlineStr"/>
       <c r="AN17" s="49" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="AI18" s="16" t="inlineStr"/>
       <c r="AN18" s="50" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       <c r="AI19" s="12" t="inlineStr"/>
       <c r="AN19" s="49" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AN20" s="50" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       <c r="AI21" s="12" t="inlineStr"/>
       <c r="AN21" s="49" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       <c r="AI22" s="16" t="inlineStr"/>
       <c r="AN22" s="50" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AN23" s="49" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       <c r="AI24" s="16" t="inlineStr"/>
       <c r="AN24" s="50" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       <c r="AI25" s="12" t="inlineStr"/>
       <c r="AN25" s="49" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AN26" s="50" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AN27" s="49" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       <c r="AI28" s="16" t="inlineStr"/>
       <c r="AN28" s="50" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       <c r="AI29" s="12" t="inlineStr"/>
       <c r="AN29" s="49" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       <c r="AI30" s="16" t="inlineStr"/>
       <c r="AN30" s="50" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="AI31" s="12" t="inlineStr"/>
       <c r="AN31" s="49" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AN32" s="50" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="AI33" s="12" t="n"/>
       <c r="AN33" s="49" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AN34" s="50" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="AI35" s="12" t="inlineStr"/>
       <c r="AN35" s="49" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AN36" s="50" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="AI37" s="12" t="inlineStr"/>
       <c r="AN37" s="49" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       <c r="AI38" s="16" t="inlineStr"/>
       <c r="AN38" s="50" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D133"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8942,6 +8942,26 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Amundi Enhanced Ultra Short Term Bond, Amundi Euro Government Bonds, Amundi Euro Liquidity Short Term Govies, Amundi Funds Emerging Markets Fund, Amundi Funds Euro Corporate Bond Select, Amundi Funds Global Corporate Bond (EURH, Amundi Funds Pioneer US Bond USD, Amundi SF Diversified, Amundi Ultra Short Term Bond Responsible, AXA IM FIS Europe Short Duration High Yi, Axa IM FIS US Corporate Interm. Bonds EU, Axa Im Fiss Europe Short Duration High Y, Candriam Bonds Credit Opportunities, Candriam Bonds Total Return, Carmignac Credit 2029, Carmignac Credit 2031, Carmignac Portfolio Flexible Bond, Carmignac Securité, Cartesius Funds Income, DNCA Alpha Bonds, DWS Deutsche Floating Rate Notes, EdR Fund Bond Allocation, CDR SICAV - Financial Bonds, Invesco Pan European High Income Fund, JPMorgan Emerging Markets Corporate Bond, Man Dynamic Income 2025, Man Dynamic Income 2026, Man Euro Corporate Bond Fund, Man Global Investment Grade Opportunitie, Muzinich Enhanced Yield Short Term, Neuberger Short Duration Emerg. Market E, Pimco Income EuroHDG, Sabadell Rendimiento Plus, Vontobel Credit Opportunities EurHdg ACC, Vontobel Fund-TwentyFour Strategic Incom</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
